--- a/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\Vanguard EU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8314E50-F054-444E-9399-D120F4C7BC11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F1307E-7216-4DBE-8C5E-8DF79F0D9066}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
   <si>
     <t>Aannames</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>World + Emerging</t>
+  </si>
+  <si>
+    <t>Dividend lek bij 2%</t>
   </si>
 </sst>
 </file>
@@ -269,11 +272,11 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -587,13 +590,13 @@
       <c r="B8" s="6"/>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="27"/>
+      <c r="B10" s="28"/>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="7"/>
@@ -768,10 +771,7 @@
         <f>G5*DividendLek!I23</f>
         <v>1.1494319636635626E-2</v>
       </c>
-      <c r="L5" s="25">
-        <f>SUM(L3:L4)</f>
-        <v>1</v>
-      </c>
+      <c r="L5" s="25"/>
       <c r="M5" s="19">
         <f>SUM(M3:M4)</f>
         <v>0.17339639130067014</v>
@@ -903,7 +903,7 @@
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="3">
@@ -917,7 +917,7 @@
       </c>
       <c r="D21" s="18"/>
       <c r="G21" s="3">
-        <f ca="1">DividendLek!I5*2.5%</f>
+        <f>DividendLek!I5*2.5%</f>
         <v>2.8556186964247415E-3</v>
       </c>
     </row>
@@ -928,7 +928,7 @@
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="G22" s="5">
-        <f ca="1">SUM(G20:G21)</f>
+        <f>SUM(G20:G21)</f>
         <v>5.2556186964247418E-3</v>
       </c>
     </row>
@@ -938,7 +938,7 @@
       <c r="D23" s="18"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G24" s="5">
@@ -965,19 +965,34 @@
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="2"/>
-      <c r="G29" s="3"/>
+      <c r="B29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="3">
+        <f>0.22%+0.02%</f>
+        <v>2.4000000000000002E-3</v>
+      </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="D30" s="18"/>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3">
+        <f>DividendLek!I5*2%</f>
+        <v>2.2844949571397934E-3</v>
+      </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="D31" s="18"/>
       <c r="E31" s="18"/>
-      <c r="G31" s="5"/>
+      <c r="G31" s="5">
+        <f>SUM(G29:G30)</f>
+        <v>4.6844949571397936E-3</v>
+      </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B32" s="17"/>
@@ -985,15 +1000,31 @@
       <c r="D32" s="18"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G33" s="5"/>
+      <c r="B33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="5">
+        <f>H6</f>
+        <v>1.4724728011107913E-3</v>
+      </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
-      <c r="G34" s="3"/>
+      <c r="B34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" s="3">
+        <f>M5*2%</f>
+        <v>3.4679278260134026E-3</v>
+      </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="2"/>
-      <c r="G35" s="5"/>
+      <c r="B35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="5">
+        <f>SUM(G33:G34)</f>
+        <v>4.9404006271241939E-3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1117,8 +1148,8 @@
         <f t="shared" si="0"/>
         <v>0.11610549719046288</v>
       </c>
-      <c r="I5" s="28">
-        <f ca="1">AVERAGE(C5:I5)</f>
+      <c r="I5" s="27">
+        <f>AVERAGE(C5:H5)</f>
         <v>0.11422474785698966</v>
       </c>
     </row>

--- a/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\Vanguard EU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F1307E-7216-4DBE-8C5E-8DF79F0D9066}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40698547-EA08-403D-BF6E-1DB436CC902D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aannames" sheetId="4" r:id="rId1"/>
@@ -35,8 +35,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={3E3CE202-C5B9-4A92-B8D2-82C869CF6CF5}</author>
+  </authors>
+  <commentList>
+    <comment ref="P11" authorId="0" shapeId="0" xr:uid="{3E3CE202-C5B9-4A92-B8D2-82C869CF6CF5}">
+      <text>
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
+    5,3% lek via trackerbelegger gepakt</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
   <si>
     <t>Aannames</t>
   </si>
@@ -128,12 +146,6 @@
     <t>Emerging</t>
   </si>
   <si>
-    <t>Emerging (GBP)</t>
-  </si>
-  <si>
-    <t>Small cap (GBP)</t>
-  </si>
-  <si>
     <t>Gemiddeld dividend na lek</t>
   </si>
   <si>
@@ -147,20 +159,42 @@
   </si>
   <si>
     <t>Dividend lek bij 2%</t>
+  </si>
+  <si>
+    <t>Bruto dividend</t>
+  </si>
+  <si>
+    <t>Belasting lek</t>
+  </si>
+  <si>
+    <t>Small cap Fund (GBP)</t>
+  </si>
+  <si>
+    <t>Emerging Fund (GBP)</t>
+  </si>
+  <si>
+    <t>Vanguard VT</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 UCITS ETF</t>
+  </si>
+  <si>
+    <t>U.S. 500 Stock Index Fund</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="0.000000000000%"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +231,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -236,7 +276,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -278,6 +318,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Komma" xfId="2" builtinId="3"/>
@@ -295,6 +336,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Gerben van Loon" id="{B39E2748-BEF5-452C-8CD9-FE69E5206B4F}" userId="S::gerben@gerbenvanloonengineering.nl::afe8845f-8ac3-4ac0-a0e6-085833b55903" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -558,6 +605,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="P11" dT="2020-08-15T07:18:50.22" personId="{B39E2748-BEF5-452C-8CD9-FE69E5206B4F}" id="{3E3CE202-C5B9-4A92-B8D2-82C869CF6CF5}">
+    <text>5,3% lek via trackerbelegger gepakt</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926ECACD-21DA-4904-B85E-A64A90D22818}">
   <dimension ref="B2:B30"/>
@@ -684,7 +739,7 @@
         <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -857,7 +912,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" s="13">
         <f>C5+C7</f>
@@ -939,7 +994,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G24" s="5">
         <f>H6</f>
@@ -975,7 +1030,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D30" s="18"/>
       <c r="G30" s="3">
@@ -1001,7 +1056,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G33" s="5">
         <f>H6</f>
@@ -1010,7 +1065,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G34" s="3">
         <f>M5*2%</f>
@@ -1034,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B4CECF-BF14-4845-8173-0C61AC18ABD7}">
-  <dimension ref="B2:I23"/>
+  <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33.28515625" customWidth="1"/>
@@ -1122,7 +1177,7 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C5" s="8">
         <f>C4/C3</f>
@@ -1235,7 +1290,7 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C11" s="8">
         <f>C10/C9</f>
@@ -1348,7 +1403,7 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C17" s="8">
         <f>C16/C15</f>
@@ -1468,7 +1523,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C23" s="8">
         <f>C22/C21</f>
@@ -1497,6 +1552,216 @@
       <c r="I23" s="24">
         <f>AVERAGE(C23:H23)</f>
         <v>0.10541081920825618</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="21">
+        <v>2014</v>
+      </c>
+      <c r="D26" s="21">
+        <v>2015</v>
+      </c>
+      <c r="E26" s="21">
+        <v>2016</v>
+      </c>
+      <c r="F26" s="21">
+        <v>2017</v>
+      </c>
+      <c r="G26" s="21">
+        <v>2018</v>
+      </c>
+      <c r="H26" s="21">
+        <v>2019</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="20">
+        <v>52371805</v>
+      </c>
+      <c r="D27" s="20">
+        <v>196059743</v>
+      </c>
+      <c r="E27" s="20">
+        <v>271884091</v>
+      </c>
+      <c r="F27" s="20">
+        <v>354919338</v>
+      </c>
+      <c r="G27" s="20">
+        <v>420900920</v>
+      </c>
+      <c r="H27" s="20">
+        <v>484099232</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="20">
+        <v>7721652</v>
+      </c>
+      <c r="D28" s="20">
+        <v>27863194</v>
+      </c>
+      <c r="E28" s="20">
+        <v>41287532</v>
+      </c>
+      <c r="F28" s="20">
+        <v>52477342</v>
+      </c>
+      <c r="G28" s="20">
+        <v>62709293</v>
+      </c>
+      <c r="H28" s="20">
+        <v>79389011</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="8">
+        <f>C28/C27</f>
+        <v>0.14743910392242543</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" ref="D29:H29" si="4">D28/D27</f>
+        <v>0.14211583455967297</v>
+      </c>
+      <c r="E29" s="8">
+        <f t="shared" si="4"/>
+        <v>0.15185710884422435</v>
+      </c>
+      <c r="F29" s="8">
+        <f t="shared" si="4"/>
+        <v>0.14785709422234974</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="4"/>
+        <v>0.1489882535775878</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="4"/>
+        <v>0.16399325954724919</v>
+      </c>
+      <c r="I29" s="19">
+        <f>AVERAGE(C29:H29)</f>
+        <v>0.15037510911225158</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="21">
+        <v>2014</v>
+      </c>
+      <c r="D32" s="21">
+        <v>2015</v>
+      </c>
+      <c r="E32" s="21">
+        <v>2016</v>
+      </c>
+      <c r="F32" s="21">
+        <v>2017</v>
+      </c>
+      <c r="G32" s="21">
+        <v>2018</v>
+      </c>
+      <c r="H32" s="21">
+        <v>2019</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="20">
+        <v>127594401</v>
+      </c>
+      <c r="D33" s="20">
+        <v>106329115</v>
+      </c>
+      <c r="E33" s="20">
+        <v>120261684</v>
+      </c>
+      <c r="F33" s="20">
+        <v>121851075</v>
+      </c>
+      <c r="G33" s="20">
+        <v>139856910</v>
+      </c>
+      <c r="H33" s="20">
+        <v>144778219</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="20">
+        <v>36349221</v>
+      </c>
+      <c r="D34" s="20">
+        <v>30258843</v>
+      </c>
+      <c r="E34" s="20">
+        <v>33504392</v>
+      </c>
+      <c r="F34" s="20">
+        <v>35980983</v>
+      </c>
+      <c r="G34" s="20">
+        <v>42860426</v>
+      </c>
+      <c r="H34" s="20">
+        <v>40550127</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="8">
+        <f>C34/C33</f>
+        <v>0.28488100351676088</v>
+      </c>
+      <c r="D35" s="8">
+        <f t="shared" ref="D35:H35" si="5">D34/D33</f>
+        <v>0.28457721104892109</v>
+      </c>
+      <c r="E35" s="8">
+        <f t="shared" si="5"/>
+        <v>0.27859573295181861</v>
+      </c>
+      <c r="F35" s="8">
+        <f t="shared" si="5"/>
+        <v>0.29528654548185151</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="5"/>
+        <v>0.30645912311375961</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="5"/>
+        <v>0.28008444419391565</v>
+      </c>
+      <c r="I35" s="19">
+        <f>AVERAGE(C35:H35)</f>
+        <v>0.28831401005117124</v>
       </c>
     </row>
   </sheetData>
@@ -1506,19 +1771,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A42A8E11-B03E-4972-9221-D29D18184BF1}">
-  <dimension ref="A2:Q15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A42A8E11-B03E-4972-9221-D29D18184BF1}">
+  <dimension ref="A2:R15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="15" max="15" width="26.42578125" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="C3" s="1">
         <v>2019</v>
@@ -1550,11 +1816,20 @@
       <c r="L3" s="1">
         <v>2010</v>
       </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M3" s="1">
+        <v>2009</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" t="s">
         <v>21</v>
@@ -1580,20 +1855,27 @@
       <c r="I4" s="5">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O4" s="5">
         <f>AVERAGE(C4:M4)</f>
         <v>2.2614285714285715E-2</v>
       </c>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P4" s="29">
+        <f>(100-(DividendLek!I5*100))/100</f>
+        <v>0.88577525214301034</v>
+      </c>
+      <c r="Q4" s="5">
+        <f>O4/P4</f>
+        <v>2.5530500721908395E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="N5" s="5"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5">
         <v>2.7099999999999999E-2</v>
@@ -1625,21 +1907,29 @@
       <c r="L6" s="5">
         <v>1.46E-2</v>
       </c>
-      <c r="N6" s="5">
-        <f t="shared" ref="N6:N9" si="0">AVERAGE(C6:M6)</f>
+      <c r="O6" s="5">
+        <f>AVERAGE(C6:M6)</f>
         <v>2.232E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P6" s="29">
+        <f>(100-(DividendLek!I23*100))/100</f>
+        <v>0.89458918079174377</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>O6/P6</f>
+        <v>2.4949999932087255E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="N7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C9" s="5">
         <v>1.84E-2</v>
@@ -1668,20 +1958,80 @@
       <c r="K9" s="5">
         <v>1.26E-2</v>
       </c>
-      <c r="N9" s="5">
-        <f t="shared" si="0"/>
+      <c r="O9" s="5">
+        <f>AVERAGE(C9:M9)</f>
         <v>1.5755555555555554E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P14" s="25"/>
-      <c r="Q14" s="18"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P15" s="25"/>
-      <c r="Q15" s="18"/>
+      <c r="P9" s="29">
+        <f>(100-(DividendLek!I17*100))/100</f>
+        <v>0.81369249079568151</v>
+      </c>
+      <c r="Q9" s="3">
+        <f t="shared" ref="Q9" si="0">O9/P9</f>
+        <v>1.9363034234405611E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="5">
+        <v>3.09E-2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2.75E-2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2.3E-2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>2.47E-2</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2.76E-2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="O11" s="5">
+        <f>AVERAGE(C11:M11)</f>
+        <v>2.467272727272727E-2</v>
+      </c>
+      <c r="P11">
+        <f>(100-5.3)/100</f>
+        <v>0.94700000000000006</v>
+      </c>
+      <c r="Q11" s="3">
+        <f>O11/P11</f>
+        <v>2.6053566285878849E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q14" s="25"/>
+      <c r="R14" s="18"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q15" s="25"/>
+      <c r="R15" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\Vanguard EU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DB46C6-D64F-473B-B4FB-F9BBDC6055C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F949FBC-6E0D-4C5B-AADB-C8436AE336E0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38535" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Totaal" sheetId="7" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Global Small-Cap" sheetId="19" r:id="rId4"/>
     <sheet name="TD" sheetId="14" r:id="rId5"/>
     <sheet name="DividendLek" sheetId="8" r:id="rId6"/>
+    <sheet name="EerderArtikel" sheetId="20" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="116">
   <si>
     <t>MSCI ACWI IMI</t>
   </si>
@@ -412,13 +413,22 @@
   </si>
   <si>
     <t>Global + Emerging 2,5% dividend</t>
+  </si>
+  <si>
+    <t>Weging</t>
+  </si>
+  <si>
+    <t>Totaal</t>
+  </si>
+  <si>
+    <t>2,5%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="44" formatCode="_ &quot;€&quot;\ * #,##0.00_ ;_ &quot;€&quot;\ * \-#,##0.00_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.000%"/>
@@ -426,6 +436,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ &quot;€&quot;\ * #,##0_ ;_ &quot;€&quot;\ * \-#,##0_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -527,7 +538,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -584,6 +595,8 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Komma" xfId="2" builtinId="3"/>
@@ -1543,6 +1556,10 @@
         <f>AVERAGE(D16:H16)</f>
         <v>0.18526885263409712</v>
       </c>
+      <c r="K16" s="5">
+        <f>AVERAGE(C16:H16)</f>
+        <v>0.18280749991867837</v>
+      </c>
       <c r="N16" s="42"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -1964,7 +1981,7 @@
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="31">
         <f>0.11%-H28+H31</f>
         <v>9.604120245493967E-4</v>
       </c>
@@ -2368,6 +2385,10 @@
         <f t="shared" si="3"/>
         <v>0.11111375552401744</v>
       </c>
+      <c r="K16" s="5">
+        <f>AVERAGE(C16:H16)</f>
+        <v>0.10541081920825618</v>
+      </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
@@ -3188,6 +3209,10 @@
       <c r="I16" s="5">
         <f>AVERAGE(D16:H16)</f>
         <v>0.18677964724011017</v>
+      </c>
+      <c r="K16" s="8">
+        <f>AVERAGE(C16:H16)</f>
+        <v>0.18630750920431849</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -5653,4 +5678,207 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18AA97E-D38E-455E-B527-87FF5E21AECB}">
+  <dimension ref="B1:J15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="44">
+        <f>Totaal!D5</f>
+        <v>0.78772395372097181</v>
+      </c>
+      <c r="C2">
+        <v>0.1</v>
+      </c>
+      <c r="D2" s="8">
+        <f>Global!K16</f>
+        <v>0.18280749991867837</v>
+      </c>
+      <c r="E2">
+        <f>B2*C2</f>
+        <v>7.8772395372097181E-2</v>
+      </c>
+      <c r="G2" s="45">
+        <f>D2*B2</f>
+        <v>0.14400184660578755</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="44">
+        <f>Totaal!D7</f>
+        <v>0.10904307283606943</v>
+      </c>
+      <c r="C3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D3" s="8">
+        <f>'Emerging Markets'!K16</f>
+        <v>0.10541081920825618</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E9" si="0">B3*C3</f>
+        <v>1.5266030197049722E-2</v>
+      </c>
+      <c r="G3" s="6">
+        <f t="shared" ref="G3:G4" si="1">D3*B3</f>
+        <v>1.1494319636635626E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="44">
+        <f>Totaal!D6</f>
+        <v>0.1032329736313204</v>
+      </c>
+      <c r="C4">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="6">
+        <f>'Global Small-Cap'!K16</f>
+        <v>0.18630750920431849</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>2.0646594726264081E-2</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="1"/>
+        <v>1.9233078185006393E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E5" s="44">
+        <f>SUM(E2:E4)</f>
+        <v>0.11468502029541099</v>
+      </c>
+      <c r="G5" s="3">
+        <f>SUM(G2:G4)</f>
+        <v>0.17472924442742957</v>
+      </c>
+      <c r="H5" s="14">
+        <f>G5*2.5%</f>
+        <v>4.3682311106857394E-3</v>
+      </c>
+      <c r="J5" s="44">
+        <f>E5+(H5*100)</f>
+        <v>0.55150813136398491</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="44"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="44">
+        <f>Totaal!E5</f>
+        <v>0.87840423476014873</v>
+      </c>
+      <c r="C8">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="8">
+        <f>D2</f>
+        <v>0.18280749991867837</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>8.7840423476014881E-2</v>
+      </c>
+      <c r="G8">
+        <f>B8*D8</f>
+        <v>0.16057888207448262</v>
+      </c>
+      <c r="J8" s="44"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="44">
+        <f>Totaal!E7</f>
+        <v>0.12159576523985123</v>
+      </c>
+      <c r="C9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D9" s="8">
+        <f>D3</f>
+        <v>0.10541081920825618</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>1.7023407133579173E-2</v>
+      </c>
+      <c r="G9">
+        <f>B9*D9</f>
+        <v>1.281750922618752E-2</v>
+      </c>
+      <c r="J9" s="44"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E10" s="44">
+        <f>SUM(E8:E9)</f>
+        <v>0.10486383060959406</v>
+      </c>
+      <c r="G10" s="6">
+        <f>SUM(G8:G9)</f>
+        <v>0.17339639130067014</v>
+      </c>
+      <c r="H10" s="14">
+        <f>G10*2.5%</f>
+        <v>4.3349097825167533E-3</v>
+      </c>
+      <c r="J10" s="44">
+        <f>E10+(H10*100)</f>
+        <v>0.53835480886126941</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J13">
+        <v>0.51700000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="44">
+        <f>J10-J13</f>
+        <v>2.1354808861269392E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\Vanguard EU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F949FBC-6E0D-4C5B-AADB-C8436AE336E0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9CF00C-5984-4C9A-90B8-1DB788CA352B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="117">
   <si>
     <t>MSCI ACWI IMI</t>
   </si>
@@ -422,6 +422,9 @@
   </si>
   <si>
     <t>2,5%</t>
+  </si>
+  <si>
+    <t>Hier wordt gehint naar optimized in het jaarverslag</t>
   </si>
 </sst>
 </file>
@@ -2295,6 +2298,9 @@
         <f t="shared" ref="I12:I31" si="3">AVERAGE(D12:H12)</f>
         <v>8.6308075121212556E-5</v>
       </c>
+      <c r="L12" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="26"/>

--- a/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-Fondsen-KostenBepaling2020.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\Vanguard EU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsen/KeuzeWelkIndexFonds/OnderzoekPerFonds/Vanguard EU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9CF00C-5984-4C9A-90B8-1DB788CA352B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7B131C08-B69E-4820-8C4F-428D00071D8B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{0A3ABF47-9428-4280-A589-D1F2FED56697}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8310" yWindow="3540" windowWidth="28800" windowHeight="15435" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Totaal" sheetId="7" r:id="rId1"/>
@@ -355,9 +355,6 @@
     <t>Staan ook overdraft kosten, maar die zie ik niet.</t>
   </si>
   <si>
-    <t>Zal wel lending feed zijn, maar die worden verrekend met lending inkomsten</t>
-  </si>
-  <si>
     <t>0,05% transaction costs</t>
   </si>
   <si>
@@ -425,6 +422,9 @@
   </si>
   <si>
     <t>Hier wordt gehint naar optimized in het jaarverslag</t>
+  </si>
+  <si>
+    <t>Zal wel lending fees zijn, maar die worden verrekend met lending inkomsten</t>
   </si>
 </sst>
 </file>
@@ -602,10 +602,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Komma" xfId="2" builtinId="3"/>
-    <cellStyle name="Procent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Valuta" xfId="3" builtinId="4"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -906,13 +906,13 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -1005,25 +1005,25 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" s="5">
         <f>Global!C40</f>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="5">
         <f>'Emerging Markets'!C40</f>
@@ -1089,12 +1089,12 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="14">
         <f>D5*C17+D6*C19+D7*C18</f>
@@ -1112,12 +1112,12 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C26" s="14">
         <f>D5*D17+D6*D19+D7*D18</f>
@@ -1126,19 +1126,19 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" s="14">
         <f>(D5*F17+D6*F19+D7*F18)*2.5%</f>
         <v>4.4334679208344841E-3</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" s="4">
         <f>SUM(C26:C27)</f>
@@ -1147,12 +1147,12 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="14">
         <f>E5*C17+E7*C18</f>
@@ -1170,12 +1170,12 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C38" s="14">
         <f>E5*D17+E7*D18</f>
@@ -1184,19 +1184,19 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C39" s="14">
         <f>(E5*F17+E7*F18)*2.5%</f>
         <v>4.4062976713640373E-3</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" s="4">
         <f>SUM(C38:C39)</f>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="I7" s="5"/>
       <c r="L7" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -2187,7 +2187,7 @@
       <c r="H8" s="23"/>
       <c r="I8" s="5"/>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
@@ -2299,7 +2299,7 @@
         <v>8.6308075121212556E-5</v>
       </c>
       <c r="L12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
@@ -2913,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="I5" s="1"/>
       <c r="L5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="I7" s="5"/>
       <c r="L7" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -3013,7 +3013,7 @@
       <c r="H8" s="22"/>
       <c r="I8" s="5"/>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
@@ -5693,25 +5693,25 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -5800,13 +5800,13 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J7" s="44"/>
     </row>
